--- a/docs/examples/campaign-playbook-import-format.xlsx
+++ b/docs/examples/campaign-playbook-import-format.xlsx
@@ -13,12 +13,12 @@
     <sheet state="visible" name="AllowedValues" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Clients!$A$1:$G$3</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Clients!$A$1:$I$3</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">Projects!$A$1:$J$3</definedName>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">Tasks!$A$1:$K$65</definedName>
     <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">ChecklistItems!$A$1:$D$152</definedName>
     <definedName hidden="1" localSheetId="5" name="_xlnm._FilterDatabase">Dependencies!$A$1:$B$26</definedName>
-    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">DataDictionary!$A$1:$G$35</definedName>
+    <definedName hidden="1" localSheetId="6" name="_xlnm._FilterDatabase">DataDictionary!$A$1:$G$37</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">AllowedValues!$A$1:$C$25</definedName>
   </definedNames>
   <calcPr/>
@@ -3264,7 +3264,9 @@
     <col customWidth="1" min="5" max="5" width="20.14"/>
     <col customWidth="1" min="6" max="6" width="33.0"/>
     <col customWidth="1" min="7" max="7" width="74.43"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
+    <col customWidth="1" min="8" max="8" width="34.43"/>
+    <col customWidth="1" min="9" max="9" width="21.57"/>
+    <col customWidth="1" min="10" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3286,8 +3288,18 @@
       <c r="F1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_source</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_id</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -3303,8 +3315,18 @@
       <c r="F2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="11" t="s">
         <v>75</v>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d3f1c62-5a47-4e8b-b0d2-7c6841ae5f30</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ghd-studio</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3320,8 +3342,18 @@
         <v>82</v>
       </c>
       <c r="F3" s="20"/>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="18" t="s">
         <v>84</v>
+      </c>
+      <c r="H3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9d3f1c62-5a47-4e8b-b0d2-7c6841ae5f30</t>
+        </is>
+      </c>
+      <c r="I3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">addrive-media</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -30802,49 +30834,77 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>388</v>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clients</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_source</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_aliases.source_namespace</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UUID text</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blank → no identity</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional; supply with client_import_id. Namespace is campaign-playbook:&lt;uuid&gt;.</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>391</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clients</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_id</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client_import_aliases.external_id</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blank → no identity</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The client's id at that source, matched exactly. An identity match wins over the name.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -30852,10 +30912,10 @@
         <v>387</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>367</v>
@@ -30867,7 +30927,7 @@
         <v>369</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12">
@@ -30875,22 +30935,22 @@
         <v>387</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>69</v>
+        <v>369</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13">
@@ -30898,22 +30958,22 @@
         <v>387</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>140</v>
+        <v>369</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14">
@@ -30921,22 +30981,22 @@
         <v>387</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>375</v>
+        <v>69</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15">
@@ -30944,22 +31004,22 @@
         <v>387</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>375</v>
+        <v>140</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16">
@@ -30967,22 +31027,22 @@
         <v>387</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>375</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17">
@@ -30990,22 +31050,22 @@
         <v>387</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>375</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18">
@@ -31013,68 +31073,68 @@
         <v>387</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>368</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>423</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21">
@@ -31082,10 +31142,10 @@
         <v>419</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>367</v>
@@ -31097,7 +31157,7 @@
         <v>369</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22">
@@ -31105,22 +31165,22 @@
         <v>419</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23">
@@ -31128,22 +31188,22 @@
         <v>419</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>155</v>
+        <v>369</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="24">
@@ -31151,10 +31211,10 @@
         <v>419</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>374</v>
@@ -31163,10 +31223,10 @@
         <v>395</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>140</v>
+        <v>375</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>400</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25">
@@ -31174,22 +31234,22 @@
         <v>419</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>375</v>
+        <v>155</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>406</v>
+        <v>437</v>
       </c>
     </row>
     <row r="26">
@@ -31197,22 +31257,22 @@
         <v>419</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>375</v>
+        <v>140</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27">
@@ -31220,22 +31280,22 @@
         <v>419</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>375</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28">
@@ -31243,22 +31303,22 @@
         <v>419</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>375</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29">
@@ -31266,68 +31326,68 @@
         <v>419</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>374</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>415</v>
+        <v>368</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>453</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>458</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>455</v>
+        <v>419</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>173</v>
+        <v>13</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>415</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32">
@@ -31335,22 +31395,22 @@
         <v>455</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>367</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>369</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="33">
@@ -31358,72 +31418,118 @@
         <v>455</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="F33" s="32" t="s">
-        <v>468</v>
+        <v>415</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>369</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>472</v>
+        <v>367</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>369</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>468</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B36" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D37" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>475</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$G$35"/>
+  <autoFilter ref="$A$1:$G$37"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
